--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -63565,13 +63565,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O352" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R352" t="n">
-        <v>0.08139473679926593</v>
+        <v>0.07945676687547389</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -64074,12 +64074,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -64113,81 +64113,100 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O355" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R355" t="n">
-        <v>0.004297557199154077</v>
+        <v>0.1308283259959668</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP355" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ355" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR355" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS355" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS355" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
       <c r="AT355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV355" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC355" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -64214,17 +64233,17 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -64249,7 +64268,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -64258,81 +64277,175 @@
         </is>
       </c>
       <c r="N356" t="n">
+        <v>14</v>
+      </c>
+      <c r="O356" t="n">
+        <v>14</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF356" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK356" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM356" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN356" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ356" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT356" t="n">
         <v>2</v>
       </c>
-      <c r="O356" t="n">
-        <v>2</v>
-      </c>
-      <c r="R356" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO356" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP356" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR356" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS356" t="inlineStr"/>
-      <c r="AT356" t="n">
-        <v>0</v>
-      </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC356" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -64364,12 +64477,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -64394,7 +64507,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -64403,93 +64516,81 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O357" t="n">
-        <v>1</v>
-      </c>
-      <c r="P357" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R357" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA357" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO357" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ357" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS357" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr"/>
       <c r="AT357" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -64516,17 +64617,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -64560,173 +64661,81 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O358" t="n">
-        <v>1</v>
-      </c>
-      <c r="P358" t="n">
-        <v>1</v>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W358" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X358" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y358" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA358" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB358" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC358" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD358" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE358" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF358" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI358" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ358" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK358" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM358" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN358" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO358" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ358" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS358" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR358" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr"/>
       <c r="AT358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV358" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC358" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -64758,12 +64767,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -64788,7 +64797,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -64797,81 +64806,93 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O359" t="n">
-        <v>19</v>
+        <v>1</v>
+      </c>
+      <c r="P359" t="n">
+        <v>1</v>
       </c>
       <c r="R359" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR359" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -64898,17 +64919,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -64933,7 +64954,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -64942,81 +64963,173 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O360" t="n">
-        <v>0</v>
-      </c>
-      <c r="R360" t="n">
-        <v>0</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P360" t="n">
+        <v>1</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM360" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN360" t="b">
+        <v>1</v>
       </c>
       <c r="AO360" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR360" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS360" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65048,12 +65161,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -65078,7 +65191,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -65087,93 +65200,81 @@
         </is>
       </c>
       <c r="N361" t="n">
+        <v>19</v>
+      </c>
+      <c r="O361" t="n">
+        <v>19</v>
+      </c>
+      <c r="R361" t="n">
+        <v>0.005443572452261832</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR361" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr"/>
+      <c r="AT361" t="n">
         <v>0</v>
       </c>
-      <c r="O361" t="n">
-        <v>0</v>
-      </c>
-      <c r="P361" t="n">
-        <v>0</v>
-      </c>
-      <c r="R361" t="n">
-        <v>0</v>
-      </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA361" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO361" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP361" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ361" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS361" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT361" t="n">
-        <v>2</v>
-      </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65200,17 +65301,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65249,168 +65350,76 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="P362" t="n">
+      <c r="R362" t="n">
         <v>0</v>
       </c>
-      <c r="U362" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W362" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X362" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y362" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA362" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB362" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC362" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD362" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE362" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF362" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG362" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI362" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ362" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK362" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM362" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN362" t="b">
-        <v>1</v>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO362" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ362" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR362" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr"/>
       <c r="AT362" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -65442,12 +65451,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -65472,7 +65481,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -65481,81 +65490,93 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O363" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0</v>
       </c>
       <c r="R363" t="n">
-        <v>0.002292030506215508</v>
+        <v>0</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR363" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS363" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65582,17 +65603,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -65617,7 +65638,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -65626,81 +65647,173 @@
         </is>
       </c>
       <c r="N364" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN364" t="b">
         <v>1</v>
       </c>
-      <c r="O364" t="n">
-        <v>1</v>
-      </c>
-      <c r="R364" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO364" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR364" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65732,12 +65845,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -65762,7 +65875,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -65771,93 +65884,81 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O365" t="n">
-        <v>2</v>
-      </c>
-      <c r="P365" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R365" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA365" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO365" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ365" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr"/>
       <c r="AT365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65884,17 +65985,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -65928,173 +66029,81 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O366" t="n">
-        <v>2</v>
-      </c>
-      <c r="P366" t="n">
-        <v>2</v>
-      </c>
-      <c r="U366" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W366" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X366" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y366" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA366" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB366" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC366" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD366" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE366" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF366" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG366" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ366" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK366" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM366" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN366" t="b">
         <v>1</v>
       </c>
+      <c r="R366" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ366" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR366" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr"/>
       <c r="AT366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66126,12 +66135,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -66156,7 +66165,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -66165,81 +66174,93 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O367" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P367" t="n">
+        <v>2</v>
       </c>
       <c r="R367" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR367" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ367" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66266,17 +66287,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -66301,7 +66322,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -66315,76 +66336,168 @@
       <c r="O368" t="n">
         <v>2</v>
       </c>
-      <c r="R368" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P368" t="n">
+        <v>2</v>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM368" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN368" t="b">
+        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR368" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ368" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66416,12 +66529,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66446,7 +66559,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -66455,93 +66568,81 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O369" t="n">
-        <v>1</v>
-      </c>
-      <c r="P369" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R369" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA369" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO369" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ369" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR369" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr"/>
       <c r="AT369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66568,17 +66669,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -66612,173 +66713,81 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O370" t="n">
-        <v>1</v>
-      </c>
-      <c r="P370" t="n">
-        <v>1</v>
-      </c>
-      <c r="U370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W370" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X370" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y370" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z370" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA370" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB370" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC370" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD370" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE370" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF370" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG370" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH370" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI370" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ370" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK370" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM370" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN370" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R370" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR370" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr"/>
       <c r="AT370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66810,12 +66819,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -66840,7 +66849,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -66849,81 +66858,93 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O371" t="n">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="P371" t="n">
+        <v>1</v>
       </c>
       <c r="R371" t="n">
-        <v>0.005157068638984894</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR371" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS371" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ371" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66950,17 +66971,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -66985,90 +67006,182 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O372" t="n">
-        <v>0</v>
-      </c>
-      <c r="R372" t="n">
-        <v>0</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P372" t="n">
+        <v>1</v>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN372" t="b">
+        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR372" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ372" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67100,12 +67213,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67130,109 +67243,90 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N373" t="n">
+        <v>18</v>
+      </c>
+      <c r="O373" t="n">
+        <v>18</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0.005157068638984894</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO373" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP373" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr"/>
+      <c r="AT373" t="n">
         <v>0</v>
       </c>
-      <c r="O373" t="n">
-        <v>0</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U373" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA373" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO373" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP373" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ373" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR373" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AT373" t="n">
-        <v>2</v>
-      </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67259,17 +67353,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67308,170 +67402,76 @@
       <c r="O374" t="n">
         <v>0</v>
       </c>
-      <c r="U374" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W374" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X374" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y374" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC374" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
+      <c r="R374" t="n">
+        <v>0</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO374" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP374" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr"/>
+      <c r="AT374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU374" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV374" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE374" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF374" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG374" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH374" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI374" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ374" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK374" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM374" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN374" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO374" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP374" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ374" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR374" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS374" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AT374" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU374" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV374" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -67503,12 +67503,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -67542,81 +67542,100 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R375" t="n">
-        <v>0.005813909771376137</v>
+        <v>0</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR375" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -67643,17 +67662,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -67692,17 +67711,34 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="R376" t="n">
-        <v>0</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U376" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -67710,6 +67746,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM376" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN376" t="b">
+        <v>1</v>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -67722,7 +67816,7 @@
       </c>
       <c r="AQ376" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR376" t="inlineStr">
@@ -67732,7 +67826,7 @@
       </c>
       <c r="AS376" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="AT376" t="n">
@@ -67740,47 +67834,47 @@
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -67807,217 +67901,526 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N377" t="n">
+        <v>8</v>
+      </c>
+      <c r="O377" t="n">
+        <v>8</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0.01550375939033637</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO377" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP377" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr"/>
+      <c r="AT377" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV377" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW377" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX377" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY377" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA377" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB377" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC377" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N378" t="n">
+        <v>0</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ378" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT378" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV378" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW378" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX378" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY378" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA378" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB378" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC378" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
+      <c r="F379" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
+      <c r="G379" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>D037</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
         <is>
           <t>疟疾</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr">
+      <c r="K379" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
+      <c r="L379" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr">
+      <c r="M379" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N377" t="n">
+      <c r="N379" t="n">
         <v>0</v>
       </c>
-      <c r="O377" t="n">
+      <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="U379" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V377" t="inlineStr">
+      <c r="V379" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="W377" t="inlineStr">
+      <c r="W379" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z377" t="inlineStr">
+      <c r="Z379" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA377" t="inlineStr">
+      <c r="AA379" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB377" t="inlineStr">
+      <c r="AB379" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC377" t="inlineStr">
+      <c r="AC379" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD377" t="inlineStr">
+      <c r="AD379" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE377" t="inlineStr">
+      <c r="AE379" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF377" t="inlineStr">
+      <c r="AF379" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG377" t="inlineStr">
+      <c r="AG379" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH377" t="inlineStr">
+      <c r="AH379" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI377" t="inlineStr">
+      <c r="AI379" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ377" t="inlineStr">
+      <c r="AJ379" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK377" t="inlineStr">
+      <c r="AK379" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM377" t="inlineStr">
+      <c r="AM379" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN377" t="b">
+      <c r="AN379" t="b">
         <v>1</v>
       </c>
-      <c r="AO377" t="inlineStr">
+      <c r="AO379" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP377" t="inlineStr">
+      <c r="AP379" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ377" t="inlineStr">
+      <c r="AQ379" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR377" t="inlineStr">
+      <c r="AR379" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS377" t="inlineStr">
+      <c r="AS379" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="AT377" t="n">
+      <c r="AT379" t="n">
         <v>2</v>
       </c>
-      <c r="AU377" t="inlineStr">
+      <c r="AU379" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV377" t="inlineStr">
+      <c r="AV379" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW377" t="inlineStr">
+      <c r="AW379" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX377" t="inlineStr">
+      <c r="AX379" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY377" t="inlineStr">
+      <c r="AY379" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ377" t="inlineStr">
+      <c r="AZ379" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA377" t="inlineStr">
+      <c r="BA379" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB377" t="inlineStr">
+      <c r="BB379" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC377" t="inlineStr">
+      <c r="BC379" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -68139,7 +68542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -68149,7 +68552,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11">
@@ -68169,7 +68572,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -68201,7 +68604,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4918</v>
+        <v>4936</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -62307,13 +62307,13 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O344" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R344" t="n">
-        <v>0.09182029548799475</v>
+        <v>0.09916591912703433</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
@@ -67358,12 +67358,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67388,22 +67388,22 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R374" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
@@ -67436,42 +67436,42 @@
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67503,12 +67503,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -67555,87 +67555,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA375" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ375" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR375" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr"/>
       <c r="AT375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -67662,7 +67643,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -67711,98 +67692,23 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
+      <c r="R376" t="n">
+        <v>0</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U376" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y376" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA376" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE376" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG376" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ376" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK376" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM376" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN376" t="b">
-        <v>1</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
@@ -67901,17 +67807,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -67945,81 +67851,175 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O377" t="n">
-        <v>8</v>
-      </c>
-      <c r="R377" t="n">
-        <v>0.01550375939033637</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM377" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN377" t="b">
+        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ377" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR377" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT377" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68051,12 +68051,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68090,100 +68090,81 @@
         </is>
       </c>
       <c r="N378" t="n">
+        <v>10</v>
+      </c>
+      <c r="O378" t="n">
+        <v>10</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0.01937969923792046</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr"/>
+      <c r="AT378" t="n">
         <v>0</v>
       </c>
-      <c r="O378" t="n">
-        <v>0</v>
-      </c>
-      <c r="R378" t="n">
-        <v>0</v>
-      </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U378" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA378" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO378" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP378" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR378" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT378" t="n">
-        <v>2</v>
-      </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -68210,7 +68191,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -68259,98 +68240,23 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U379" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W379" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y379" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC379" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD379" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE379" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG379" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM379" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN379" t="b">
-        <v>1</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -68421,6 +68327,245 @@
         </is>
       </c>
       <c r="BC379" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0</v>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM380" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN380" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO380" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP380" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ380" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR380" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT380" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU380" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV380" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW380" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX380" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY380" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA380" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB380" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC380" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -68542,7 +68687,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -68552,7 +68697,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11">
@@ -68604,7 +68749,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4936</v>
+        <v>4941</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -62307,13 +62307,13 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O344" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R344" t="n">
-        <v>0.09916591912703433</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
@@ -63710,13 +63710,13 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O353" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R353" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -63874,10 +63874,10 @@
         </is>
       </c>
       <c r="N354" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O354" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U354" t="inlineStr">
         <is>
@@ -68090,13 +68090,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O378" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R378" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -68235,13 +68235,13 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R379" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -68399,10 +68399,10 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U380" t="inlineStr">
         <is>
@@ -68749,7 +68749,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4941</v>
+        <v>4945</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -63123,12 +63123,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -63162,100 +63162,84 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>6</v>
+        <v>445</v>
       </c>
       <c r="O350" t="n">
-        <v>6</v>
+        <v>445</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>1</v>
       </c>
       <c r="R350" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.03149519164837743</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA350" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO350" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP350" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ350" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR350" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS350" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr"/>
       <c r="AT350" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV350" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ350" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA350" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB350" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC350" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -63282,7 +63266,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -63331,98 +63315,23 @@
       <c r="O351" t="n">
         <v>6</v>
       </c>
+      <c r="R351" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U351" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
-      <c r="V351" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W351" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X351" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y351" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z351" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA351" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB351" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC351" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD351" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE351" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF351" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG351" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH351" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI351" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ351" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK351" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM351" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN351" t="b">
-        <v>1</v>
       </c>
       <c r="AO351" t="inlineStr">
         <is>
@@ -63521,17 +63430,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -63565,81 +63474,175 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="O352" t="n">
-        <v>41</v>
-      </c>
-      <c r="R352" t="n">
-        <v>0.07945676687547389</v>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK352" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM352" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN352" t="b">
+        <v>1</v>
       </c>
       <c r="AO352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR352" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS352" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ352" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA352" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB352" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC352" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -63671,12 +63674,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -63710,100 +63713,81 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O353" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="R353" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.07945676687547389</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA353" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO353" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ353" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR353" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS353" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr"/>
       <c r="AT353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV353" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ353" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA353" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB353" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC353" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -63830,7 +63814,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -63879,98 +63863,23 @@
       <c r="O354" t="n">
         <v>8</v>
       </c>
+      <c r="R354" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U354" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W354" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X354" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y354" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA354" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB354" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC354" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD354" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE354" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF354" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI354" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ354" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK354" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM354" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN354" t="b">
-        <v>1</v>
       </c>
       <c r="AO354" t="inlineStr">
         <is>
@@ -64069,17 +63978,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -64113,22 +64022,39 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O355" t="n">
-        <v>14</v>
-      </c>
-      <c r="R355" t="n">
-        <v>0.1308283259959668</v>
-      </c>
-      <c r="S355" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -64136,6 +64062,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB355" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD355" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE355" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF355" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI355" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ355" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK355" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM355" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN355" t="b">
+        <v>1</v>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -64158,7 +64142,7 @@
       </c>
       <c r="AS355" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT355" t="n">
@@ -64171,42 +64155,42 @@
       </c>
       <c r="AV355" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC355" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -64233,7 +64217,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -64282,98 +64266,23 @@
       <c r="O356" t="n">
         <v>14</v>
       </c>
+      <c r="R356" t="n">
+        <v>0.1308283259959668</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U356" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MALARIA</t>
         </is>
       </c>
-      <c r="V356" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
-        </is>
-      </c>
-      <c r="W356" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X356" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y356" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z356" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA356" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB356" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC356" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD356" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE356" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF356" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG356" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI356" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ356" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK356" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM356" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN356" t="b">
-        <v>1</v>
       </c>
       <c r="AO356" t="inlineStr">
         <is>
@@ -64472,17 +64381,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -64516,81 +64425,175 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O357" t="n">
-        <v>15</v>
-      </c>
-      <c r="R357" t="n">
-        <v>0.004297557199154077</v>
-      </c>
-      <c r="S357" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM357" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN357" t="b">
+        <v>1</v>
       </c>
       <c r="AO357" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ357" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR357" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS357" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
       <c r="AT357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -64622,12 +64625,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -64652,7 +64655,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -64661,13 +64664,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O358" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R358" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -64700,42 +64703,42 @@
       </c>
       <c r="AV358" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC358" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -64767,12 +64770,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -64806,93 +64809,81 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O359" t="n">
-        <v>1</v>
-      </c>
-      <c r="P359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R359" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA359" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO359" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ359" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr"/>
       <c r="AT359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -64919,7 +64910,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -64971,98 +64962,18 @@
       <c r="P360" t="n">
         <v>1</v>
       </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V360" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W360" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X360" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y360" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R360" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC360" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD360" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE360" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF360" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG360" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI360" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ360" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK360" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM360" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN360" t="b">
-        <v>1</v>
       </c>
       <c r="AO360" t="inlineStr">
         <is>
@@ -65156,17 +65067,17 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -65191,7 +65102,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -65200,81 +65111,173 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O361" t="n">
-        <v>19</v>
-      </c>
-      <c r="R361" t="n">
-        <v>0.005443572452261832</v>
-      </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P361" t="n">
+        <v>1</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM361" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN361" t="b">
+        <v>1</v>
       </c>
       <c r="AO361" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR361" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS361" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT361" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65306,12 +65309,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65336,7 +65339,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -65345,13 +65348,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O362" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R362" t="n">
-        <v>0</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -65384,42 +65387,42 @@
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65451,12 +65454,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -65495,9 +65498,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="P363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -65506,77 +65506,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA363" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO363" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ363" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS363" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr"/>
       <c r="AT363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -65603,7 +65594,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -65655,98 +65646,18 @@
       <c r="P364" t="n">
         <v>0</v>
       </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X364" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y364" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC364" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD364" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE364" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF364" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI364" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ364" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK364" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM364" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN364" t="b">
-        <v>1</v>
       </c>
       <c r="AO364" t="inlineStr">
         <is>
@@ -65840,17 +65751,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -65875,7 +65786,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -65884,81 +65795,173 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O365" t="n">
-        <v>8</v>
-      </c>
-      <c r="R365" t="n">
-        <v>0.002292030506215508</v>
-      </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN365" t="b">
+        <v>1</v>
       </c>
       <c r="AO365" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR365" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS365" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ365" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65990,12 +65993,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -66020,7 +66023,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -66029,13 +66032,13 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O366" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R366" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -66068,42 +66071,42 @@
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66135,12 +66138,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -66174,93 +66177,81 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O367" t="n">
-        <v>2</v>
-      </c>
-      <c r="P367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R367" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA367" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO367" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ367" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR367" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr"/>
       <c r="AT367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66287,7 +66278,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -66339,98 +66330,18 @@
       <c r="P368" t="n">
         <v>2</v>
       </c>
-      <c r="U368" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W368" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y368" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R368" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB368" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC368" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD368" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE368" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF368" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG368" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ368" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK368" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM368" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN368" t="b">
-        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
@@ -66524,17 +66435,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66559,7 +66470,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -66568,81 +66479,173 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O369" t="n">
-        <v>14</v>
-      </c>
-      <c r="R369" t="n">
-        <v>0.00401105338587714</v>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P369" t="n">
+        <v>2</v>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM369" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN369" t="b">
+        <v>1</v>
       </c>
       <c r="AO369" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR369" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ369" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66674,12 +66677,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -66704,7 +66707,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -66713,13 +66716,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O370" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R370" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -66752,42 +66755,42 @@
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66819,12 +66822,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -66858,93 +66861,81 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O371" t="n">
-        <v>1</v>
-      </c>
-      <c r="P371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R371" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA371" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO371" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ371" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS371" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR371" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr"/>
       <c r="AT371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66971,7 +66962,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -67023,98 +67014,18 @@
       <c r="P372" t="n">
         <v>1</v>
       </c>
-      <c r="U372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X372" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y372" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R372" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB372" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC372" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD372" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE372" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF372" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG372" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ372" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK372" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM372" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN372" t="b">
-        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
@@ -67208,17 +67119,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67243,7 +67154,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -67252,81 +67163,173 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O373" t="n">
-        <v>18</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0.005157068638984894</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P373" t="n">
+        <v>1</v>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM373" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN373" t="b">
+        <v>1</v>
       </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR373" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ373" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67358,12 +67361,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67388,7 +67391,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -67397,13 +67400,13 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O374" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R374" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.005157068638984894</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
@@ -67436,42 +67439,42 @@
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67503,12 +67506,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -67533,22 +67536,22 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R375" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
@@ -67581,42 +67584,42 @@
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67648,12 +67651,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -67678,12 +67681,12 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N376" t="n">
@@ -67692,6 +67695,9 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
+      <c r="P376" t="n">
+        <v>0</v>
+      </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
@@ -67700,14 +67706,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO376" t="inlineStr">
@@ -67717,22 +67718,17 @@
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ376" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR376" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS376" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_190</t>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
         </is>
       </c>
       <c r="AT376" t="n">
@@ -67740,47 +67736,47 @@
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67812,12 +67808,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -67842,12 +67838,12 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N377" t="n">
@@ -67856,19 +67852,22 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
+      <c r="P377" t="n">
+        <v>0</v>
+      </c>
       <c r="U377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_190</t>
+          <t>SER_SG_CDA_MALARIA</t>
         </is>
       </c>
       <c r="V377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_190</t>
+          <t>SER_SG_CDA_MALARIA</t>
         </is>
       </c>
       <c r="W377" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X377" t="inlineStr">
@@ -67883,12 +67882,12 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB377" t="inlineStr">
@@ -67898,7 +67897,7 @@
       </c>
       <c r="AC377" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD377" t="inlineStr">
@@ -67933,12 +67932,12 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM377" t="inlineStr">
@@ -67956,22 +67955,17 @@
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ377" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR377" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_190</t>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
         </is>
       </c>
       <c r="AT377" t="n">
@@ -67979,47 +67973,47 @@
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68051,12 +68045,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68090,13 +68084,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O378" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R378" t="n">
-        <v>0.0251936090092966</v>
+        <v>0</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -68129,42 +68123,42 @@
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -68196,12 +68190,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -68235,13 +68229,13 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R379" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -68250,7 +68244,7 @@
       </c>
       <c r="U379" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -68270,7 +68264,7 @@
       </c>
       <c r="AQ379" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR379" t="inlineStr">
@@ -68280,7 +68274,7 @@
       </c>
       <c r="AS379" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="AT379" t="n">
@@ -68288,47 +68282,47 @@
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68360,12 +68354,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68399,24 +68393,24 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U380" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="V380" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="W380" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X380" t="inlineStr">
@@ -68446,7 +68440,7 @@
       </c>
       <c r="AC380" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD380" t="inlineStr">
@@ -68481,17 +68475,17 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
         </is>
       </c>
       <c r="AM380" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN380" t="b">
@@ -68509,7 +68503,7 @@
       </c>
       <c r="AQ380" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR380" t="inlineStr">
@@ -68519,7 +68513,7 @@
       </c>
       <c r="AS380" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="AT380" t="n">
@@ -68527,47 +68521,740 @@
       </c>
       <c r="AU380" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV380" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW380" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX380" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY380" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA380" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB380" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC380" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>13</v>
+      </c>
+      <c r="O381" t="n">
+        <v>13</v>
+      </c>
+      <c r="R381" t="n">
+        <v>0.0251936090092966</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr"/>
+      <c r="AT381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU381" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV381" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW381" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX381" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY381" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA381" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB381" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC381" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>1</v>
+      </c>
+      <c r="O382" t="n">
+        <v>1</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO382" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP382" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ382" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT382" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU382" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV380" t="inlineStr">
+      <c r="AV382" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW380" t="inlineStr">
+      <c r="AW382" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX380" t="inlineStr">
+      <c r="AX382" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY380" t="inlineStr">
+      <c r="AY382" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ380" t="inlineStr">
+      <c r="AZ382" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA380" t="inlineStr">
+      <c r="BA382" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB380" t="inlineStr">
+      <c r="BB382" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC380" t="inlineStr">
+      <c r="BC382" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>1</v>
+      </c>
+      <c r="O383" t="n">
+        <v>1</v>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF383" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG383" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH383" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI383" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ383" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK383" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM383" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN383" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO383" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP383" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ383" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT383" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU383" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV383" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW383" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX383" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY383" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA383" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB383" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC383" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>21</v>
+      </c>
+      <c r="O384" t="n">
+        <v>21</v>
+      </c>
+      <c r="R384" t="n">
+        <v>0.006016580078815709</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
+      <c r="AT384" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU384" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -68604,7 +69291,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -68687,7 +69374,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -68697,7 +69384,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -68717,7 +69404,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -68749,7 +69436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4945</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="16">
@@ -68759,7 +69446,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -68632,13 +68632,13 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O381" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R381" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -69436,7 +69436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5411</v>
+        <v>5414</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -57937,13 +57937,13 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O319" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R319" t="n">
-        <v>0.1608515036747398</v>
+        <v>0.1589135337509478</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -68632,13 +68632,13 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O381" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R381" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -69255,6 +69255,151 @@
       <c r="BC384" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR385" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr"/>
+      <c r="AT385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU385" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV385" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW385" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX385" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA385" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB385" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC385" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69291,7 +69436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -69374,7 +69519,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -69384,7 +69529,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
@@ -69436,7 +69581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5414</v>
+        <v>5416</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -64222,12 +64222,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -64261,13 +64261,13 @@
         </is>
       </c>
       <c r="N356" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O356" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R356" t="n">
-        <v>0.1308283259959668</v>
+        <v>0.1134756279883097</v>
       </c>
       <c r="S356" t="inlineStr">
         <is>
@@ -64276,7 +64276,7 @@
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -64291,7 +64291,7 @@
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ356" t="inlineStr">
@@ -64299,62 +64299,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR356" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS356" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC356" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -64386,12 +64381,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -64425,24 +64420,24 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O357" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="V357" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="W357" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X357" t="inlineStr">
@@ -64457,7 +64452,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -64472,7 +64467,7 @@
       </c>
       <c r="AC357" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD357" t="inlineStr">
@@ -64507,17 +64502,17 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly malaria notifications.</t>
         </is>
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN357" t="b">
@@ -64530,7 +64525,7 @@
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ357" t="inlineStr">
@@ -64538,62 +64533,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR357" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS357" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -64625,12 +64615,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -64664,81 +64654,100 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O358" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R358" t="n">
-        <v>0.004297557199154077</v>
+        <v>0.1308283259959668</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ358" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR358" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS358" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
       <c r="AT358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV358" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC358" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -64765,17 +64774,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -64800,7 +64809,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -64809,81 +64818,175 @@
         </is>
       </c>
       <c r="N359" t="n">
+        <v>14</v>
+      </c>
+      <c r="O359" t="n">
+        <v>14</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM359" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN359" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT359" t="n">
         <v>2</v>
       </c>
-      <c r="O359" t="n">
-        <v>2</v>
-      </c>
-      <c r="R359" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO359" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP359" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR359" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr"/>
-      <c r="AT359" t="n">
-        <v>0</v>
-      </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -64915,12 +65018,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -64945,7 +65048,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -64954,93 +65057,81 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O360" t="n">
-        <v>1</v>
-      </c>
-      <c r="P360" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R360" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA360" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO360" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ360" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS360" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr"/>
       <c r="AT360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65067,17 +65158,17 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -65111,173 +65202,81 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O361" t="n">
-        <v>1</v>
-      </c>
-      <c r="P361" t="n">
-        <v>1</v>
-      </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W361" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X361" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y361" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA361" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB361" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC361" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD361" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE361" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF361" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI361" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ361" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK361" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM361" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN361" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R361" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO361" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ361" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS361" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR361" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr"/>
       <c r="AT361" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -65309,12 +65308,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65339,7 +65338,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -65348,81 +65347,93 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O362" t="n">
-        <v>19</v>
+        <v>1</v>
+      </c>
+      <c r="P362" t="n">
+        <v>1</v>
       </c>
       <c r="R362" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR362" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65449,17 +65460,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -65484,7 +65495,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -65493,81 +65504,173 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O363" t="n">
-        <v>0</v>
-      </c>
-      <c r="R363" t="n">
-        <v>0</v>
-      </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P363" t="n">
+        <v>1</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM363" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN363" t="b">
+        <v>1</v>
       </c>
       <c r="AO363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR363" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS363" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65599,12 +65702,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -65629,7 +65732,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -65638,93 +65741,81 @@
         </is>
       </c>
       <c r="N364" t="n">
+        <v>19</v>
+      </c>
+      <c r="O364" t="n">
+        <v>19</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0.005443572452261832</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="n">
         <v>0</v>
       </c>
-      <c r="O364" t="n">
-        <v>0</v>
-      </c>
-      <c r="P364" t="n">
-        <v>0</v>
-      </c>
-      <c r="R364" t="n">
-        <v>0</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA364" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO364" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP364" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ364" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT364" t="n">
-        <v>2</v>
-      </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65751,17 +65842,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -65800,168 +65891,76 @@
       <c r="O365" t="n">
         <v>0</v>
       </c>
-      <c r="P365" t="n">
+      <c r="R365" t="n">
         <v>0</v>
       </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X365" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y365" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA365" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB365" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC365" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD365" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE365" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ365" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK365" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM365" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN365" t="b">
-        <v>1</v>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO365" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ365" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr"/>
       <c r="AT365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -65993,12 +65992,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -66023,7 +66022,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -66032,81 +66031,93 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O366" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="P366" t="n">
+        <v>0</v>
       </c>
       <c r="R366" t="n">
-        <v>0.002292030506215508</v>
+        <v>0</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR366" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ366" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66133,17 +66144,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -66168,7 +66179,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -66177,81 +66188,173 @@
         </is>
       </c>
       <c r="N367" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0</v>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM367" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN367" t="b">
         <v>1</v>
       </c>
-      <c r="O367" t="n">
-        <v>1</v>
-      </c>
-      <c r="R367" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR367" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ367" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66283,12 +66386,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -66313,7 +66416,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -66322,93 +66425,81 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O368" t="n">
-        <v>2</v>
-      </c>
-      <c r="P368" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R368" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA368" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO368" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ368" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR368" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr"/>
       <c r="AT368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66435,17 +66526,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66479,173 +66570,81 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O369" t="n">
-        <v>2</v>
-      </c>
-      <c r="P369" t="n">
-        <v>2</v>
-      </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W369" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X369" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y369" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z369" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA369" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB369" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC369" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD369" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE369" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF369" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG369" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ369" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK369" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM369" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN369" t="b">
         <v>1</v>
       </c>
+      <c r="R369" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ369" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR369" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr"/>
       <c r="AT369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66677,12 +66676,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -66707,7 +66706,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -66716,81 +66715,93 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O370" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P370" t="n">
+        <v>2</v>
       </c>
       <c r="R370" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR370" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ370" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66817,17 +66828,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -66852,7 +66863,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -66866,76 +66877,168 @@
       <c r="O371" t="n">
         <v>2</v>
       </c>
-      <c r="R371" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S371" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P371" t="n">
+        <v>2</v>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF371" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH371" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI371" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ371" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK371" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM371" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN371" t="b">
+        <v>1</v>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR371" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS371" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ371" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66967,12 +67070,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -66997,7 +67100,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -67006,93 +67109,81 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O372" t="n">
-        <v>1</v>
-      </c>
-      <c r="P372" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R372" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S372" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA372" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ372" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR372" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr"/>
       <c r="AT372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67119,17 +67210,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67163,173 +67254,81 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O373" t="n">
-        <v>1</v>
-      </c>
-      <c r="P373" t="n">
-        <v>1</v>
-      </c>
-      <c r="U373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W373" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X373" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y373" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z373" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA373" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB373" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC373" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD373" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE373" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF373" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG373" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ373" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK373" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM373" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN373" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ373" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr"/>
       <c r="AT373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67361,12 +67360,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67391,7 +67390,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -67400,81 +67399,93 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O374" t="n">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="P374" t="n">
+        <v>1</v>
       </c>
       <c r="R374" t="n">
-        <v>0.005157068638984894</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR374" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS374" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ374" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT374" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67501,17 +67512,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -67536,7 +67547,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -67550,76 +67561,168 @@
       <c r="O375" t="n">
         <v>1</v>
       </c>
-      <c r="R375" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S375" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P375" t="n">
+        <v>1</v>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ375" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK375" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM375" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN375" t="b">
+        <v>1</v>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR375" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67651,12 +67754,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -67681,7 +67784,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -67690,93 +67793,81 @@
         </is>
       </c>
       <c r="N376" t="n">
+        <v>18</v>
+      </c>
+      <c r="O376" t="n">
+        <v>18</v>
+      </c>
+      <c r="R376" t="n">
+        <v>0.005157068638984894</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO376" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP376" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR376" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr"/>
+      <c r="AT376" t="n">
         <v>0</v>
       </c>
-      <c r="O376" t="n">
-        <v>0</v>
-      </c>
-      <c r="P376" t="n">
-        <v>0</v>
-      </c>
-      <c r="R376" t="n">
-        <v>0</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA376" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO376" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP376" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ376" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT376" t="n">
-        <v>2</v>
-      </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67803,17 +67894,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -67847,173 +67938,81 @@
         </is>
       </c>
       <c r="N377" t="n">
+        <v>1</v>
+      </c>
+      <c r="O377" t="n">
+        <v>1</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO377" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP377" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr"/>
+      <c r="AT377" t="n">
         <v>0</v>
       </c>
-      <c r="O377" t="n">
-        <v>0</v>
-      </c>
-      <c r="P377" t="n">
-        <v>0</v>
-      </c>
-      <c r="U377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W377" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z377" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA377" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB377" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC377" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD377" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE377" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG377" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ377" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK377" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM377" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN377" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO377" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP377" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ377" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT377" t="n">
-        <v>2</v>
-      </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68045,12 +68044,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68075,12 +68074,12 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N378" t="n">
@@ -68089,6 +68088,9 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
+      <c r="P378" t="n">
+        <v>0</v>
+      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -68097,68 +68099,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR378" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ378" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68185,17 +68196,17 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -68220,12 +68231,12 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N379" t="n">
@@ -68234,23 +68245,101 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="R379" t="n">
+      <c r="P379" t="n">
         <v>0</v>
       </c>
-      <c r="S379" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U379" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_190</t>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF379" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG379" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI379" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ379" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK379" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM379" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN379" t="b">
+        <v>1</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -68259,22 +68348,17 @@
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ379" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR379" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS379" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_190</t>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
         </is>
       </c>
       <c r="AT379" t="n">
@@ -68282,47 +68366,47 @@
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68349,17 +68433,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68398,170 +68482,76 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="U380" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W380" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X380" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y380" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z380" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA380" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB380" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC380" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD380" t="inlineStr">
+      <c r="R380" t="n">
+        <v>0</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO380" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP380" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR380" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr"/>
+      <c r="AT380" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU380" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV380" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE380" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF380" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG380" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ380" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK380" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM380" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN380" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO380" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP380" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ380" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR380" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS380" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AT380" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU380" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV380" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -68593,12 +68583,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -68632,81 +68622,100 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O381" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R381" t="n">
-        <v>0.03682142855204888</v>
+        <v>0</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ381" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR381" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS381" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68733,17 +68742,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -68777,29 +68786,104 @@
         </is>
       </c>
       <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF382" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK382" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM382" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN382" t="b">
         <v>1</v>
       </c>
-      <c r="O382" t="n">
-        <v>1</v>
-      </c>
-      <c r="R382" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U382" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA382" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68812,7 +68896,7 @@
       </c>
       <c r="AQ382" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR382" t="inlineStr">
@@ -68822,7 +68906,7 @@
       </c>
       <c r="AS382" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="AT382" t="n">
@@ -68830,47 +68914,47 @@
       </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68897,17 +68981,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -68941,175 +69025,81 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O383" t="n">
-        <v>1</v>
-      </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W383" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X383" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y383" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z383" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA383" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC383" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD383" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE383" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF383" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG383" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH383" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI383" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ383" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK383" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM383" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN383" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0.0465112781710091</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ383" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR383" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
       <c r="AT383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -69141,12 +69131,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -69171,7 +69161,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -69180,81 +69170,100 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O384" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R384" t="n">
-        <v>0.006016580078815709</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ384" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR384" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS384" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA384" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB384" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC384" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -69281,123 +69290,507 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>1</v>
+      </c>
+      <c r="O385" t="n">
+        <v>1</v>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF385" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ385" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK385" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM385" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN385" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP385" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ385" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR385" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU385" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV385" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW385" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX385" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA385" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB385" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC385" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>21</v>
+      </c>
+      <c r="O386" t="n">
+        <v>21</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0.006016580078815709</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR386" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr"/>
+      <c r="AT386" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU386" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV386" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW386" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX386" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY386" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA386" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB386" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC386" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
+      <c r="G387" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>D037</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
         <is>
           <t>疟疾</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
+      <c r="K387" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
+      <c r="L387" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr">
+      <c r="M387" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N385" t="n">
+      <c r="N387" t="n">
         <v>0</v>
       </c>
-      <c r="O385" t="n">
+      <c r="O387" t="n">
         <v>0</v>
       </c>
-      <c r="R385" t="n">
+      <c r="R387" t="n">
         <v>0</v>
       </c>
-      <c r="S385" t="inlineStr">
+      <c r="S387" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO385" t="inlineStr">
+      <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP385" t="inlineStr">
+      <c r="AP387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR385" t="inlineStr">
+      <c r="AR387" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS385" t="inlineStr"/>
-      <c r="AT385" t="n">
+      <c r="AS387" t="inlineStr"/>
+      <c r="AT387" t="n">
         <v>0</v>
       </c>
-      <c r="AU385" t="inlineStr">
+      <c r="AU387" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV385" t="inlineStr">
+      <c r="AV387" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW385" t="inlineStr">
+      <c r="AW387" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX385" t="inlineStr">
+      <c r="AX387" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY385" t="inlineStr">
+      <c r="AY387" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ385" t="inlineStr">
+      <c r="AZ387" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA385" t="inlineStr">
+      <c r="BA387" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB385" t="inlineStr">
+      <c r="BB387" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC385" t="inlineStr">
+      <c r="BC387" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -69519,7 +69912,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -69529,7 +69922,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11">
@@ -69549,7 +69942,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -69581,7 +69974,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5416</v>
+        <v>5427</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -68622,13 +68622,13 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R381" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -68786,10 +68786,10 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U382" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5427</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -69025,13 +69025,13 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O383" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R383" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S383" t="inlineStr">
         <is>
@@ -69793,6 +69793,545 @@
       <c r="BC387" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>2</v>
+      </c>
+      <c r="O388" t="n">
+        <v>2</v>
+      </c>
+      <c r="P388" t="n">
+        <v>2</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO388" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP388" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ388" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT388" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU388" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV388" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW388" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX388" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY388" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA388" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB388" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC388" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>2</v>
+      </c>
+      <c r="O389" t="n">
+        <v>2</v>
+      </c>
+      <c r="P389" t="n">
+        <v>2</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM389" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN389" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO389" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP389" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ389" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS389" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT389" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU389" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV389" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW389" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX389" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY389" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA389" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB389" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC389" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>11</v>
+      </c>
+      <c r="O390" t="n">
+        <v>11</v>
+      </c>
+      <c r="R390" t="n">
+        <v>0.003151541946046324</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO390" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP390" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR390" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr"/>
+      <c r="AT390" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU390" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV390" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW390" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX390" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY390" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA390" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB390" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC390" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -69829,7 +70368,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -69912,7 +70451,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -69922,7 +70461,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11">
@@ -69942,7 +70481,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -69974,7 +70513,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5428</v>
+        <v>5442</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -63713,13 +63713,13 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O353" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R353" t="n">
-        <v>0.07945676687547389</v>
+        <v>0.08139473679926593</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -70513,7 +70513,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5442</v>
+        <v>5443</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -62307,13 +62307,13 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O344" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R344" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.09916591912703433</v>
       </c>
       <c r="S344" t="inlineStr">
         <is>
@@ -63674,12 +63674,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -63713,13 +63713,13 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="O353" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="R353" t="n">
-        <v>0.08139473679926593</v>
+        <v>0.04065810840590128</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -63752,42 +63752,42 @@
       </c>
       <c r="AV353" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ353" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA353" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB353" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC353" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -63819,12 +63819,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -63858,100 +63858,81 @@
         </is>
       </c>
       <c r="N354" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O354" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="R354" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.07945676687547389</v>
       </c>
       <c r="S354" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA354" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO354" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ354" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR354" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS354" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr"/>
       <c r="AT354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ354" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA354" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB354" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC354" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -63978,7 +63959,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -64027,98 +64008,23 @@
       <c r="O355" t="n">
         <v>8</v>
       </c>
+      <c r="R355" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U355" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W355" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X355" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y355" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z355" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA355" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB355" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC355" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD355" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE355" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF355" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG355" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI355" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ355" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK355" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM355" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN355" t="b">
-        <v>1</v>
       </c>
       <c r="AO355" t="inlineStr">
         <is>
@@ -64217,17 +64123,17 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -64261,22 +64167,39 @@
         </is>
       </c>
       <c r="N356" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O356" t="n">
-        <v>6</v>
-      </c>
-      <c r="R356" t="n">
-        <v>0.1134756279883097</v>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>SER_NZ_MALARIA_MONTHLY</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -64284,6 +64207,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF356" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK356" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM356" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN356" t="b">
+        <v>1</v>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -64291,7 +64272,7 @@
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ356" t="inlineStr">
@@ -64299,57 +64280,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS356" t="inlineStr">
         <is>
-          <t>SER_NZ_MALARIA_MONTHLY</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC356" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -64376,7 +64362,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -64425,98 +64411,23 @@
       <c r="O357" t="n">
         <v>6</v>
       </c>
+      <c r="R357" t="n">
+        <v>0.1134756279883097</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U357" t="inlineStr">
         <is>
           <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
-      <c r="V357" t="inlineStr">
-        <is>
-          <t>SER_NZ_MALARIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W357" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X357" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y357" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA357" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB357" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC357" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD357" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE357" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF357" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG357" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI357" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ357" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK357" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly malaria notifications.</t>
-        </is>
-      </c>
-      <c r="AM357" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN357" t="b">
-        <v>1</v>
       </c>
       <c r="AO357" t="inlineStr">
         <is>
@@ -64610,17 +64521,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -64654,22 +64565,39 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O358" t="n">
-        <v>14</v>
-      </c>
-      <c r="R358" t="n">
-        <v>0.1308283259959668</v>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -64677,6 +64605,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ358" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK358" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly malaria notifications.</t>
+        </is>
+      </c>
+      <c r="AM358" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN358" t="b">
+        <v>1</v>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -64684,7 +64670,7 @@
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ358" t="inlineStr">
@@ -64692,62 +64678,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR358" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS358" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV358" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC358" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -64774,7 +64755,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -64823,98 +64804,23 @@
       <c r="O359" t="n">
         <v>14</v>
       </c>
+      <c r="R359" t="n">
+        <v>0.1308283259959668</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U359" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MALARIA</t>
         </is>
       </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
-        </is>
-      </c>
-      <c r="W359" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X359" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y359" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA359" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB359" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC359" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD359" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE359" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF359" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI359" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ359" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK359" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM359" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN359" t="b">
-        <v>1</v>
       </c>
       <c r="AO359" t="inlineStr">
         <is>
@@ -65013,17 +64919,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -65057,81 +64963,175 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O360" t="n">
-        <v>15</v>
-      </c>
-      <c r="R360" t="n">
-        <v>0.004297557199154077</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM360" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN360" t="b">
+        <v>1</v>
       </c>
       <c r="AO360" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR360" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS360" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
       <c r="AT360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -65163,12 +65163,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -65193,7 +65193,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -65202,13 +65202,13 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O361" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R361" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S361" t="inlineStr">
         <is>
@@ -65241,42 +65241,42 @@
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65308,12 +65308,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65347,93 +65347,81 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O362" t="n">
-        <v>1</v>
-      </c>
-      <c r="P362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R362" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA362" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO362" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ362" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR362" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr"/>
       <c r="AT362" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -65460,7 +65448,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -65512,98 +65500,18 @@
       <c r="P363" t="n">
         <v>1</v>
       </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V363" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X363" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y363" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R363" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB363" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC363" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD363" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE363" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF363" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG363" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI363" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ363" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK363" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM363" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN363" t="b">
-        <v>1</v>
       </c>
       <c r="AO363" t="inlineStr">
         <is>
@@ -65697,17 +65605,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -65732,7 +65640,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -65741,81 +65649,173 @@
         </is>
       </c>
       <c r="N364" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O364" t="n">
-        <v>19</v>
-      </c>
-      <c r="R364" t="n">
-        <v>0.005443572452261832</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P364" t="n">
+        <v>1</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN364" t="b">
+        <v>1</v>
       </c>
       <c r="AO364" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR364" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -65847,12 +65847,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -65877,7 +65877,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -65886,13 +65886,13 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O365" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R365" t="n">
-        <v>0</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -65925,42 +65925,42 @@
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -65992,12 +65992,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -66036,9 +66036,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="P366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -66047,77 +66044,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA366" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO366" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ366" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR366" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr"/>
       <c r="AT366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66144,7 +66132,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -66196,98 +66184,18 @@
       <c r="P367" t="n">
         <v>0</v>
       </c>
-      <c r="U367" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W367" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X367" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y367" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z367" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R367" t="n">
+        <v>0</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB367" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC367" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD367" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE367" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF367" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG367" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH367" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI367" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ367" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK367" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM367" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN367" t="b">
-        <v>1</v>
       </c>
       <c r="AO367" t="inlineStr">
         <is>
@@ -66381,17 +66289,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -66416,7 +66324,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -66425,81 +66333,173 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O368" t="n">
-        <v>8</v>
-      </c>
-      <c r="R368" t="n">
-        <v>0.002292030506215508</v>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0</v>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM368" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN368" t="b">
+        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR368" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ368" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66531,12 +66531,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66561,7 +66561,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -66570,13 +66570,13 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O369" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R369" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
@@ -66609,42 +66609,42 @@
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66676,12 +66676,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -66715,93 +66715,81 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O370" t="n">
-        <v>2</v>
-      </c>
-      <c r="P370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R370" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA370" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR370" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr"/>
       <c r="AT370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66828,7 +66816,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -66880,98 +66868,18 @@
       <c r="P371" t="n">
         <v>2</v>
       </c>
-      <c r="U371" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W371" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X371" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y371" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R371" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC371" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD371" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE371" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF371" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG371" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH371" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI371" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ371" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK371" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM371" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN371" t="b">
-        <v>1</v>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
@@ -67065,17 +66973,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -67100,7 +67008,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -67109,81 +67017,173 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O372" t="n">
-        <v>14</v>
-      </c>
-      <c r="R372" t="n">
-        <v>0.00401105338587714</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P372" t="n">
+        <v>2</v>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN372" t="b">
+        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR372" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ372" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67215,12 +67215,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67245,7 +67245,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -67254,13 +67254,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O373" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R373" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
@@ -67293,42 +67293,42 @@
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67360,12 +67360,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67399,93 +67399,81 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O374" t="n">
-        <v>1</v>
-      </c>
-      <c r="P374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R374" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ374" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr"/>
       <c r="AT374" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67512,7 +67500,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -67564,98 +67552,18 @@
       <c r="P375" t="n">
         <v>1</v>
       </c>
-      <c r="U375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W375" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X375" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y375" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R375" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD375" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE375" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF375" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG375" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH375" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI375" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ375" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK375" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM375" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN375" t="b">
-        <v>1</v>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
@@ -67749,17 +67657,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -67784,7 +67692,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -67793,81 +67701,173 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O376" t="n">
-        <v>18</v>
-      </c>
-      <c r="R376" t="n">
-        <v>0.005157068638984894</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P376" t="n">
+        <v>1</v>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM376" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN376" t="b">
+        <v>1</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR376" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ376" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67899,12 +67899,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -67929,7 +67929,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -67938,13 +67938,13 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O377" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R377" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.005157068638984894</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
@@ -67977,42 +67977,42 @@
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -68044,12 +68044,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68083,93 +68083,81 @@
         </is>
       </c>
       <c r="N378" t="n">
+        <v>1</v>
+      </c>
+      <c r="O378" t="n">
+        <v>1</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr"/>
+      <c r="AT378" t="n">
         <v>0</v>
       </c>
-      <c r="O378" t="n">
-        <v>0</v>
-      </c>
-      <c r="P378" t="n">
-        <v>0</v>
-      </c>
-      <c r="R378" t="n">
-        <v>0</v>
-      </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA378" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO378" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP378" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT378" t="n">
-        <v>2</v>
-      </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68196,7 +68184,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -68248,98 +68236,18 @@
       <c r="P379" t="n">
         <v>0</v>
       </c>
-      <c r="U379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W379" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y379" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC379" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD379" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE379" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG379" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM379" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN379" t="b">
-        <v>1</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -68433,17 +68341,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68468,12 +68376,12 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N380" t="n">
@@ -68482,76 +68390,168 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="R380" t="n">
+      <c r="P380" t="n">
         <v>0</v>
       </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM380" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN380" t="b">
+        <v>1</v>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR380" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS380" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ380" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT380" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68583,12 +68583,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -68622,100 +68622,81 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R381" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA381" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO381" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ381" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR381" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS381" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr"/>
       <c r="AT381" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -68742,7 +68723,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -68786,103 +68767,28 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O382" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U382" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
-      <c r="V382" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W382" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X382" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y382" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z382" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA382" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB382" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC382" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD382" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE382" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF382" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG382" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH382" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI382" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ382" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK382" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM382" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN382" t="b">
-        <v>1</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
@@ -68981,17 +68887,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -69025,81 +68931,175 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="O383" t="n">
-        <v>25</v>
-      </c>
-      <c r="R383" t="n">
-        <v>0.04844924809480115</v>
-      </c>
-      <c r="S383" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF383" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG383" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH383" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI383" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ383" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK383" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM383" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN383" t="b">
+        <v>1</v>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ383" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR383" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -69131,12 +69131,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -69170,100 +69170,81 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O384" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R384" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05232518794238524</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA384" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO384" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ384" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR384" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS384" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
       <c r="AT384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA384" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB384" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC384" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -69290,7 +69271,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -69334,103 +69315,28 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O385" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U385" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W385" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X385" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y385" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA385" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB385" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC385" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD385" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE385" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF385" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG385" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH385" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI385" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ385" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK385" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM385" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN385" t="b">
-        <v>1</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
@@ -69529,17 +69435,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -69564,7 +69470,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -69573,81 +69479,175 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O386" t="n">
-        <v>21</v>
-      </c>
-      <c r="R386" t="n">
-        <v>0.006016580078815709</v>
-      </c>
-      <c r="S386" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM386" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN386" t="b">
+        <v>1</v>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP386" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ386" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR386" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS386" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU386" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV386" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA386" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB386" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC386" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -69679,12 +69679,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -69709,7 +69709,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -69718,13 +69718,13 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O387" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R387" t="n">
-        <v>0</v>
+        <v>0.006016580078815709</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -69757,42 +69757,42 @@
       </c>
       <c r="AV387" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA387" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB387" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC387" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -69824,12 +69824,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -69863,93 +69863,81 @@
         </is>
       </c>
       <c r="N388" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O388" t="n">
-        <v>2</v>
-      </c>
-      <c r="P388" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R388" t="n">
-        <v>0.03386531510194095</v>
+        <v>0</v>
       </c>
       <c r="S388" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA388" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO388" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP388" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ388" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS388" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR388" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr"/>
       <c r="AT388" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU388" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV388" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA388" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB388" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC388" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69976,7 +69964,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -70028,98 +70016,18 @@
       <c r="P389" t="n">
         <v>2</v>
       </c>
-      <c r="U389" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W389" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X389" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y389" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R389" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC389" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD389" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE389" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF389" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG389" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH389" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI389" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ389" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK389" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM389" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN389" t="b">
-        <v>1</v>
       </c>
       <c r="AO389" t="inlineStr">
         <is>
@@ -70213,123 +70121,1044 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>2</v>
+      </c>
+      <c r="O390" t="n">
+        <v>2</v>
+      </c>
+      <c r="P390" t="n">
+        <v>2</v>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF390" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG390" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH390" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI390" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ390" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK390" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM390" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN390" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO390" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP390" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ390" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT390" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU390" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV390" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW390" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX390" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY390" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA390" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB390" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC390" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
+      <c r="F391" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
+      <c r="G391" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>D037</t>
-        </is>
-      </c>
-      <c r="I390" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="J390" t="inlineStr">
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
         <is>
           <t>疟疾</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr">
+      <c r="K391" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
+      <c r="L391" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr">
+      <c r="M391" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N390" t="n">
+      <c r="N391" t="n">
         <v>11</v>
       </c>
-      <c r="O390" t="n">
+      <c r="O391" t="n">
         <v>11</v>
       </c>
-      <c r="R390" t="n">
+      <c r="R391" t="n">
         <v>0.003151541946046324</v>
       </c>
-      <c r="S390" t="inlineStr">
+      <c r="S391" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO390" t="inlineStr">
+      <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP390" t="inlineStr">
+      <c r="AP391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR390" t="inlineStr">
+      <c r="AR391" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS390" t="inlineStr"/>
-      <c r="AT390" t="n">
+      <c r="AS391" t="inlineStr"/>
+      <c r="AT391" t="n">
         <v>0</v>
       </c>
-      <c r="AU390" t="inlineStr">
+      <c r="AU391" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV390" t="inlineStr">
+      <c r="AV391" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW390" t="inlineStr">
+      <c r="AW391" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX390" t="inlineStr">
+      <c r="AX391" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY390" t="inlineStr">
+      <c r="AY391" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ390" t="inlineStr">
+      <c r="AZ391" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA390" t="inlineStr">
+      <c r="BA391" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB390" t="inlineStr">
+      <c r="BB391" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC390" t="inlineStr">
+      <c r="BC391" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" t="n">
+        <v>0</v>
+      </c>
+      <c r="R392" t="n">
+        <v>0</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO392" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP392" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR392" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr"/>
+      <c r="AT392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU392" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV392" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW392" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX392" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY392" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA392" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB392" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC392" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>1</v>
+      </c>
+      <c r="O393" t="n">
+        <v>1</v>
+      </c>
+      <c r="P393" t="n">
+        <v>1</v>
+      </c>
+      <c r="R393" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO393" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP393" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ393" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS393" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT393" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU393" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV393" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW393" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX393" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY393" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA393" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB393" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC393" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>1</v>
+      </c>
+      <c r="O394" t="n">
+        <v>1</v>
+      </c>
+      <c r="P394" t="n">
+        <v>1</v>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ394" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK394" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM394" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN394" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP394" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ394" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV394" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW394" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX394" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY394" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA394" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB394" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC394" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>8</v>
+      </c>
+      <c r="O395" t="n">
+        <v>8</v>
+      </c>
+      <c r="R395" t="n">
+        <v>0.002292030506215508</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP395" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR395" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr"/>
+      <c r="AT395" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV395" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW395" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX395" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY395" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA395" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB395" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC395" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -70368,7 +71197,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -70451,7 +71280,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -70461,7 +71290,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -70481,7 +71310,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -70513,7 +71342,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5443</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -66938,13 +66938,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O370" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R370" t="n">
-        <v>0.07945676687547389</v>
+        <v>0.07751879695168185</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -71702,13 +71702,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O397" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R397" t="n">
-        <v>0</v>
+        <v>0.06243780093183643</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -72250,13 +72250,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="O400" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="R400" t="n">
-        <v>0.05232518794238524</v>
+        <v>0.07558082702788979</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -74241,6 +74241,1238 @@
       <c r="BC411" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO412" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP412" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR412" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr"/>
+      <c r="AT412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV412" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW412" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX412" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY412" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA412" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB412" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC412" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+      <c r="R413" t="n">
+        <v>0</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO413" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP413" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT413" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU413" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV413" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW413" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX413" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY413" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA413" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB413" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC413" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0</v>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB414" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC414" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD414" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE414" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG414" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI414" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ414" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK414" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM414" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN414" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO414" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP414" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ414" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT414" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU414" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV414" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW414" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX414" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY414" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA414" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB414" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC414" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>15</v>
+      </c>
+      <c r="O415" t="n">
+        <v>15</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0.004297557199154077</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO415" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP415" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR415" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr"/>
+      <c r="AT415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU415" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV415" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW415" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX415" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY415" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA415" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB415" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC415" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0</v>
+      </c>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO416" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP416" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ416" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR416" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS416" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="AT416" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU416" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV416" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW416" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX416" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY416" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA416" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB416" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC416" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB417" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC417" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD417" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE417" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF417" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG417" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH417" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI417" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ417" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK417" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM417" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN417" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO417" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP417" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ417" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR417" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="AT417" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU417" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV417" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW417" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX417" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY417" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA417" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB417" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC417" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO418" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP418" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR418" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr"/>
+      <c r="AT418" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU418" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV418" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW418" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX418" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY418" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA418" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB418" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC418" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -74277,7 +75509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -74360,7 +75592,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
@@ -74370,7 +75602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11">
@@ -74390,7 +75622,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -74422,7 +75654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5641</v>
+        <v>5684</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -71702,13 +71702,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O397" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="R397" t="n">
-        <v>0.06243780093183643</v>
+        <v>0.08447467184895517</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -72250,13 +72250,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O400" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R400" t="n">
-        <v>0.07558082702788979</v>
+        <v>0.07751879695168185</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -75654,7 +75654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5684</v>
+        <v>5691</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -22648,7 +22648,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -31215,7 +31215,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -39770,7 +39770,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -49195,7 +49195,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -58723,7 +58723,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="AM372" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN372" t="b">
@@ -72651,7 +72651,7 @@
       </c>
       <c r="AM402" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN402" t="b">
